--- a/Test Case google home page.xlsx
+++ b/Test Case google home page.xlsx
@@ -17,9 +17,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>TC_Practical-001</t>
   </si>
   <si>
     <t>Test Case Desc</t>
@@ -246,6 +243,9 @@
   </si>
   <si>
     <t>Test the Login Functionality of Google Home Page</t>
+  </si>
+  <si>
+    <t>TC_Practical-006</t>
   </si>
 </sst>
 </file>
@@ -733,8 +733,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -742,15 +742,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -762,19 +775,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1050,24 +1050,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="40"/>
       <c r="C1" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20" t="s">
-        <v>2</v>
+      <c r="E1" s="21"/>
+      <c r="F1" s="45" t="s">
+        <v>68</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -1085,27 +1085,27 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
-        <v>3</v>
+      <c r="A2" s="46" t="s">
+        <v>2</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="23" t="s">
         <v>65</v>
-      </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="29"/>
-      <c r="J2" s="23" t="s">
-        <v>66</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1124,23 +1124,23 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="29"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="24"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1187,22 +1187,22 @@
     </row>
     <row r="5" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="31"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1225,17 +1225,17 @@
         <v>1</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="9"/>
       <c r="F6" s="10">
         <v>1</v>
       </c>
       <c r="G6" s="28"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="31"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1258,17 +1258,17 @@
         <v>2</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10">
         <v>2</v>
       </c>
       <c r="G7" s="28"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
       <c r="J7" s="31"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1291,17 +1291,17 @@
         <v>3</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10">
         <v>3</v>
       </c>
       <c r="G8" s="28"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
       <c r="J8" s="31"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1379,19 +1379,19 @@
     </row>
     <row r="11" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
-      <c r="B11" s="45" t="s">
-        <v>67</v>
+      <c r="B11" s="36" t="s">
+        <v>66</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1410,15 +1410,15 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1464,25 +1464,25 @@
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="C14" s="40"/>
+      <c r="D14" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="48" t="s">
+      <c r="E14" s="40"/>
+      <c r="F14" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="48" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="39"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="40"/>
+      <c r="J14" s="42"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1503,17 +1503,17 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="49" t="s">
-        <v>63</v>
+      <c r="B15" s="43" t="s">
+        <v>62</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
-      <c r="E15" s="29"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="28"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="28"/>
       <c r="J15" s="31"/>
       <c r="K15" s="1"/>
@@ -1537,16 +1537,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="29"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
       <c r="I16" s="28"/>
       <c r="J16" s="31"/>
       <c r="K16" s="1"/>
@@ -1570,16 +1570,16 @@
         <v>3</v>
       </c>
       <c r="B17" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="29"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30"/>
       <c r="I17" s="28"/>
       <c r="J17" s="31"/>
       <c r="K17" s="1"/>
@@ -1603,16 +1603,16 @@
         <v>4</v>
       </c>
       <c r="B18" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="29"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30"/>
       <c r="I18" s="28"/>
       <c r="J18" s="31"/>
       <c r="K18" s="1"/>
@@ -1636,16 +1636,16 @@
         <v>5</v>
       </c>
       <c r="B19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="29"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="28"/>
       <c r="J19" s="31"/>
       <c r="K19" s="1"/>
@@ -1669,16 +1669,16 @@
         <v>6</v>
       </c>
       <c r="B20" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="28"/>
       <c r="J20" s="31"/>
       <c r="K20" s="1"/>
@@ -1702,16 +1702,16 @@
         <v>7</v>
       </c>
       <c r="B21" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="28"/>
       <c r="J21" s="31"/>
       <c r="K21" s="1"/>
@@ -1735,16 +1735,16 @@
         <v>8</v>
       </c>
       <c r="B22" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="28"/>
       <c r="J22" s="31"/>
       <c r="K22" s="1"/>
@@ -1768,16 +1768,16 @@
         <v>9</v>
       </c>
       <c r="B23" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="28"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="28"/>
       <c r="J23" s="31"/>
       <c r="K23" s="1"/>
@@ -1801,16 +1801,16 @@
         <v>10</v>
       </c>
       <c r="B24" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="28"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="28"/>
       <c r="J24" s="31"/>
       <c r="K24" s="1"/>
@@ -1834,16 +1834,16 @@
         <v>11</v>
       </c>
       <c r="B25" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="28"/>
       <c r="J25" s="31"/>
       <c r="K25" s="1"/>
@@ -1867,16 +1867,16 @@
         <v>12</v>
       </c>
       <c r="B26" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30"/>
       <c r="I26" s="28"/>
       <c r="J26" s="31"/>
       <c r="K26" s="1"/>
@@ -1900,16 +1900,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="28"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30"/>
       <c r="I27" s="28"/>
       <c r="J27" s="31"/>
       <c r="K27" s="1"/>
@@ -1933,16 +1933,16 @@
         <v>14</v>
       </c>
       <c r="B28" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="29"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="28"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="28"/>
       <c r="J28" s="31"/>
       <c r="K28" s="1"/>
@@ -1966,16 +1966,16 @@
         <v>15</v>
       </c>
       <c r="B29" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="29"/>
+      <c r="E29" s="30"/>
       <c r="F29" s="28"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="28"/>
       <c r="J29" s="31"/>
       <c r="K29" s="1"/>
@@ -1999,16 +1999,16 @@
         <v>16</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="30"/>
       <c r="F30" s="28"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="28"/>
       <c r="J30" s="31"/>
       <c r="K30" s="1"/>
@@ -2032,16 +2032,16 @@
         <v>17</v>
       </c>
       <c r="B31" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="29"/>
+      <c r="E31" s="30"/>
       <c r="F31" s="28"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="30"/>
       <c r="I31" s="28"/>
       <c r="J31" s="31"/>
       <c r="K31" s="1"/>
@@ -2065,16 +2065,16 @@
         <v>18</v>
       </c>
       <c r="B32" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="29"/>
+      <c r="E32" s="30"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="28"/>
       <c r="J32" s="31"/>
       <c r="K32" s="1"/>
@@ -2098,16 +2098,16 @@
         <v>19</v>
       </c>
       <c r="B33" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="29"/>
+      <c r="E33" s="30"/>
       <c r="F33" s="28"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="30"/>
       <c r="I33" s="28"/>
       <c r="J33" s="31"/>
       <c r="K33" s="1"/>
@@ -2131,11 +2131,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="33"/>
       <c r="D34" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="33"/>
       <c r="F34" s="32"/>
@@ -2164,16 +2164,16 @@
         <v>21</v>
       </c>
       <c r="B35" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="29"/>
+      <c r="E35" s="30"/>
       <c r="F35" s="28"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="28"/>
       <c r="J35" s="31"/>
       <c r="K35" s="4"/>
@@ -2197,11 +2197,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="33"/>
       <c r="D36" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="32"/>
@@ -28093,6 +28093,94 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B24:C24"/>
@@ -28117,94 +28205,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
